--- a/region/San-Antonio-overview-grid.xlsx
+++ b/region/San-Antonio-overview-grid.xlsx
@@ -112,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD62"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — San Antonio — generated 8/28/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — San Antonio — generated 9/15/2026</t>
         </is>
       </c>
     </row>
@@ -324,8 +324,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -426,8 +434,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -505,7 +521,7 @@
       <c r="W5" s="9"/>
       <c r="X5" s="5"/>
       <c r="Y5" s="5">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="Z5" s="13" t="inlineStr">
         <is>
@@ -520,7 +536,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">004157</t>
+          <t xml:space="preserve">004225</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -530,12 +546,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -545,17 +561,17 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">320538</t>
+          <t xml:space="preserve">320628</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 N WS 0.9mi N/O Loop 410 F/S - 1</t>
+          <t xml:space="preserve">US 90 NS 0.2mi E/O Hwy 151 F/W - 1</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -565,18 +581,18 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78233</t>
+          <t xml:space="preserve">78237</t>
         </is>
       </c>
       <c r="K6" s="10">
-        <v>29.531573</v>
+        <v>29.407858</v>
       </c>
       <c r="L6" s="10">
-        <v>-98.391567</v>
+        <v>-98.583545</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -607,15 +623,15 @@
         </is>
       </c>
       <c r="U6" s="4">
-        <v>685058</v>
+        <v>196832</v>
       </c>
       <c r="V6" s="8">
-        <v>1500</v>
+        <v>2700</v>
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z6" s="12" t="inlineStr">
         <is>
@@ -630,7 +646,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">004225</t>
+          <t xml:space="preserve">004364</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -640,12 +656,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -660,12 +676,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">320628</t>
+          <t xml:space="preserve">320845</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">US 90 NS 0.2mi E/O Hwy 151 F/W - 1</t>
+          <t xml:space="preserve">US 281 N ES 0.2mi N/O Pasa Del Norte F/S - 2</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -675,23 +691,23 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78237</t>
+          <t xml:space="preserve">78232</t>
         </is>
       </c>
       <c r="K7" s="11">
-        <v>29.407858</v>
+        <v>29.58611</v>
       </c>
       <c r="L7" s="11">
-        <v>-98.583545</v>
+        <v>-98.474459</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
@@ -717,15 +733,15 @@
         </is>
       </c>
       <c r="U7" s="5">
-        <v>196832</v>
+        <v>318759</v>
       </c>
       <c r="V7" s="9">
-        <v>2700</v>
+        <v>1400</v>
       </c>
       <c r="W7" s="9"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="5">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="Z7" s="13" t="inlineStr">
         <is>
@@ -740,7 +756,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">004364</t>
+          <t xml:space="preserve">004413</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -748,8 +764,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -762,12 +786,12 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">320845</t>
+          <t xml:space="preserve">320935</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">US 281 N ES 0.2mi N/O Pasa Del Norte F/S - 2</t>
+          <t xml:space="preserve">I-35 S ES 0.3mi N/O SW Military F/N - 1</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -777,25 +801,21 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78232</t>
+          <t xml:space="preserve">78221</t>
         </is>
       </c>
       <c r="K8" s="10">
-        <v>29.58611</v>
+        <v>29.362253</v>
       </c>
       <c r="L8" s="10">
-        <v>-98.474459</v>
+        <v>-98.521554</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N8" s="4"/>
       <c r="O8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -819,15 +839,15 @@
         </is>
       </c>
       <c r="U8" s="4">
-        <v>318759</v>
+        <v>156948</v>
       </c>
       <c r="V8" s="8">
-        <v>1400</v>
+        <v>3312.5</v>
       </c>
       <c r="W8" s="8"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" s="12" t="inlineStr">
         <is>
@@ -842,7 +862,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">004413</t>
+          <t xml:space="preserve">004664</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -850,8 +870,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -859,17 +887,17 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">320935</t>
+          <t xml:space="preserve">321296</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 S ES 0.3mi N/O SW Military F/N - 1</t>
+          <t xml:space="preserve">Loop 410 SS 50ft W/O Jackson Keller F/E - 1</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -879,21 +907,25 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78221</t>
+          <t xml:space="preserve">78213</t>
         </is>
       </c>
       <c r="K9" s="11">
-        <v>29.362253</v>
+        <v>29.515748</v>
       </c>
       <c r="L9" s="11">
-        <v>-98.521554</v>
+        <v>-98.528158</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
-        </is>
-      </c>
-      <c r="N9" s="5"/>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -917,15 +949,15 @@
         </is>
       </c>
       <c r="U9" s="5">
-        <v>156948</v>
+        <v>909209</v>
       </c>
       <c r="V9" s="9">
-        <v>3312.5</v>
+        <v>4770</v>
       </c>
       <c r="W9" s="9"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="5">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="Z9" s="13" t="inlineStr">
         <is>
@@ -940,7 +972,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">004664</t>
+          <t xml:space="preserve">004697</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -948,8 +980,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -957,17 +997,17 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321296</t>
+          <t xml:space="preserve">321343</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 410 SS 50ft W/O Jackson Keller F/E - 1</t>
+          <t xml:space="preserve">Loop 410 NS 0.3mi E/O Perrin Beitel F/W - 1</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -977,18 +1017,18 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78213</t>
+          <t xml:space="preserve">78217</t>
         </is>
       </c>
       <c r="K10" s="10">
-        <v>29.515748</v>
+        <v>29.516817</v>
       </c>
       <c r="L10" s="10">
-        <v>-98.528158</v>
+        <v>-98.405618</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1008,7 +1048,7 @@
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="6">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="S10" s="6">
         <v>46327</v>
@@ -1019,15 +1059,15 @@
         </is>
       </c>
       <c r="U10" s="4">
-        <v>909209</v>
+        <v>552954</v>
       </c>
       <c r="V10" s="8">
-        <v>4770</v>
+        <v>1500</v>
       </c>
       <c r="W10" s="8"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4">
-        <v>0.1</v>
+        <v>2.1</v>
       </c>
       <c r="Z10" s="12" t="inlineStr">
         <is>
@@ -1050,8 +1090,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1129,7 +1177,7 @@
       <c r="W11" s="9"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="5">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" s="13" t="inlineStr">
         <is>
@@ -1152,8 +1200,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1231,7 +1287,7 @@
       <c r="W12" s="8"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" s="12" t="inlineStr">
         <is>
@@ -1254,8 +1310,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1352,8 +1416,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1450,8 +1522,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1554,12 +1634,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1662,8 +1742,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1756,7 +1844,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">005184</t>
+          <t xml:space="preserve">005185</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1764,8 +1852,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1778,12 +1874,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321722</t>
+          <t xml:space="preserve">321723</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">McAllister Frwy WS 0.1mi N/O Sunset F/S - 1</t>
+          <t xml:space="preserve">McAllister Frwy WS 0.1mi N/O Sunset F/N - 2</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1804,14 +1900,10 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N18" s="4"/>
       <c r="O18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -1824,10 +1916,10 @@
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="6">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="S18" s="6">
-        <v>46278</v>
+        <v>46327</v>
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
@@ -1835,7 +1927,7 @@
         </is>
       </c>
       <c r="U18" s="4">
-        <v>419410</v>
+        <v>332709</v>
       </c>
       <c r="V18" s="8">
         <v>3312.5</v>
@@ -1843,7 +1935,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" s="12" t="inlineStr">
         <is>
@@ -1858,7 +1950,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">005185</t>
+          <t xml:space="preserve">005188</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1866,8 +1958,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -1880,12 +1980,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321723</t>
+          <t xml:space="preserve">321726</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">McAllister Frwy WS 0.1mi N/O Sunset F/N - 2</t>
+          <t xml:space="preserve">I-10 NW WS 0.3mi S/O DeZavala F/N - 2</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1895,14 +1995,14 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78216</t>
+          <t xml:space="preserve">78249</t>
         </is>
       </c>
       <c r="K19" s="11">
-        <v>29.508447</v>
+        <v>29.558421</v>
       </c>
       <c r="L19" s="11">
-        <v>-98.478278</v>
+        <v>-98.590158</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -1922,7 +2022,7 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="7">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="S19" s="7">
         <v>46327</v>
@@ -1933,7 +2033,7 @@
         </is>
       </c>
       <c r="U19" s="5">
-        <v>332709</v>
+        <v>1095078</v>
       </c>
       <c r="V19" s="9">
         <v>3312.5</v>
@@ -1941,7 +2041,7 @@
       <c r="W19" s="9"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Z19" s="13" t="inlineStr">
         <is>
@@ -1956,7 +2056,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">005187</t>
+          <t xml:space="preserve">005403</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -1966,12 +2066,12 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1981,17 +2081,17 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321725</t>
+          <t xml:space="preserve">321821</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-10 NW WS 0.3mi S/O DeZavala F/S - 1</t>
+          <t xml:space="preserve">Loop 410 SS 0.2mi W/O Jackson Keller F/W - 2</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2001,23 +2101,23 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78249</t>
+          <t xml:space="preserve">78213</t>
         </is>
       </c>
       <c r="K20" s="10">
-        <v>29.558421</v>
+        <v>29.514349</v>
       </c>
       <c r="L20" s="10">
-        <v>-98.590158</v>
+        <v>-98.530145</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">W</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -2032,10 +2132,10 @@
       </c>
       <c r="Q20" s="4"/>
       <c r="R20" s="6">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="S20" s="6">
-        <v>46278</v>
+        <v>46327</v>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
@@ -2043,10 +2143,10 @@
         </is>
       </c>
       <c r="U20" s="4">
-        <v>439287</v>
+        <v>1034308</v>
       </c>
       <c r="V20" s="8">
-        <v>3312.5</v>
+        <v>4500</v>
       </c>
       <c r="W20" s="8"/>
       <c r="X20" s="4"/>
@@ -2066,7 +2166,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">005188</t>
+          <t xml:space="preserve">005430</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2074,8 +2174,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2083,17 +2191,17 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321726</t>
+          <t xml:space="preserve">321845</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-10 NW WS 0.3mi S/O DeZavala F/N - 2</t>
+          <t xml:space="preserve">San Pedro ES 0.3mi N/O Jackson Keller F/S - 2</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -2103,21 +2211,25 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78249</t>
+          <t xml:space="preserve">78216</t>
         </is>
       </c>
       <c r="K21" s="11">
-        <v>29.558421</v>
+        <v>29.500712</v>
       </c>
       <c r="L21" s="11">
-        <v>-98.590158</v>
+        <v>-98.498884</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
-        </is>
-      </c>
-      <c r="N21" s="5"/>
+          <t xml:space="preserve">S</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -2130,7 +2242,7 @@
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="7">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="S21" s="7">
         <v>46327</v>
@@ -2141,15 +2253,15 @@
         </is>
       </c>
       <c r="U21" s="5">
-        <v>1095078</v>
+        <v>131668</v>
       </c>
       <c r="V21" s="9">
-        <v>3312.5</v>
+        <v>2800</v>
       </c>
       <c r="W21" s="9"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" s="13" t="inlineStr">
         <is>
@@ -2164,7 +2276,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">005403</t>
+          <t xml:space="preserve">005437</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2172,8 +2284,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2186,12 +2306,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321821</t>
+          <t xml:space="preserve">321851</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 410 SS 0.2mi W/O Jackson Keller F/W - 2</t>
+          <t xml:space="preserve">I-10 E NS 1.5mi E/O Foster Rd F/E - 2</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2201,18 +2321,18 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78213</t>
+          <t xml:space="preserve">78109</t>
         </is>
       </c>
       <c r="K22" s="10">
-        <v>29.514349</v>
+        <v>29.455148</v>
       </c>
       <c r="L22" s="10">
-        <v>-98.530145</v>
+        <v>-98.331176</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2232,7 +2352,7 @@
       </c>
       <c r="Q22" s="4"/>
       <c r="R22" s="6">
-        <v>46279</v>
+        <v>46300</v>
       </c>
       <c r="S22" s="6">
         <v>46327</v>
@@ -2243,15 +2363,15 @@
         </is>
       </c>
       <c r="U22" s="4">
-        <v>1034308</v>
+        <v>207445</v>
       </c>
       <c r="V22" s="8">
-        <v>4500</v>
+        <v>2000</v>
       </c>
       <c r="W22" s="8"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" s="12" t="inlineStr">
         <is>
@@ -2266,7 +2386,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">005430</t>
+          <t xml:space="preserve">005540</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2274,8 +2394,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2288,12 +2416,12 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321845</t>
+          <t xml:space="preserve">321897</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Pedro ES 0.3mi N/O Jackson Keller F/S - 2</t>
+          <t xml:space="preserve">Blanco ES 0.5mi S/O Loop 1604 F/N - 1</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -2303,23 +2431,23 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78216</t>
+          <t xml:space="preserve">78232</t>
         </is>
       </c>
       <c r="K23" s="11">
-        <v>29.500712</v>
+        <v>29.599146</v>
       </c>
       <c r="L23" s="11">
-        <v>-98.498884</v>
+        <v>-98.508815</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2334,7 +2462,7 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="7">
-        <v>46293</v>
+        <v>46258</v>
       </c>
       <c r="S23" s="7">
         <v>46327</v>
@@ -2345,15 +2473,15 @@
         </is>
       </c>
       <c r="U23" s="5">
-        <v>131668</v>
+        <v>79381</v>
       </c>
       <c r="V23" s="9">
-        <v>2800</v>
+        <v>1900</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="13" t="inlineStr">
         <is>
@@ -2368,7 +2496,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">005437</t>
+          <t xml:space="preserve">005569</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2376,8 +2504,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2385,17 +2521,17 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321851</t>
+          <t xml:space="preserve">321922</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-10 E NS 1.5mi E/O Foster Rd F/E - 2</t>
+          <t xml:space="preserve">Loop 1604 WS 0.9mi N/O Culebra F/N - 2</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2405,18 +2541,18 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78109</t>
+          <t xml:space="preserve">78254</t>
         </is>
       </c>
       <c r="K24" s="10">
-        <v>29.455148</v>
+        <v>29.501489</v>
       </c>
       <c r="L24" s="10">
-        <v>-98.331176</v>
+        <v>-98.702068</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2436,7 +2572,7 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="6">
-        <v>46300</v>
+        <v>46258</v>
       </c>
       <c r="S24" s="6">
         <v>46327</v>
@@ -2447,10 +2583,10 @@
         </is>
       </c>
       <c r="U24" s="4">
-        <v>207445</v>
+        <v>279692</v>
       </c>
       <c r="V24" s="8">
-        <v>2000</v>
+        <v>5500</v>
       </c>
       <c r="W24" s="8"/>
       <c r="X24" s="4"/>
@@ -2470,7 +2606,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">005540</t>
+          <t xml:space="preserve">005606</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2478,8 +2614,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2492,12 +2636,12 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321897</t>
+          <t xml:space="preserve">321953</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blanco ES 0.5mi S/O Loop 1604 F/N - 1</t>
+          <t xml:space="preserve">Potranco NS 0.2mi W/O W Military F/E - 2</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -2507,23 +2651,23 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78232</t>
+          <t xml:space="preserve">78251</t>
         </is>
       </c>
       <c r="K25" s="11">
-        <v>29.599146</v>
+        <v>29.449667</v>
       </c>
       <c r="L25" s="11">
-        <v>-98.508815</v>
+        <v>-98.647585</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -2538,7 +2682,7 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="7">
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="S25" s="7">
         <v>46327</v>
@@ -2549,15 +2693,15 @@
         </is>
       </c>
       <c r="U25" s="5">
-        <v>79381</v>
+        <v>159466</v>
       </c>
       <c r="V25" s="9">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="W25" s="9"/>
       <c r="X25" s="5"/>
       <c r="Y25" s="5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Z25" s="13" t="inlineStr">
         <is>
@@ -2572,7 +2716,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">005569</t>
+          <t xml:space="preserve">010206</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2582,12 +2726,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2597,34 +2741,34 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321922</t>
+          <t xml:space="preserve">30706737</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 1604 WS 0.9mi N/O Culebra F/N - 2</t>
+          <t xml:space="preserve">US281 N WS 700ft S/O Thousand Oaks F/N</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Hollywood park</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78254</t>
+          <t xml:space="preserve">78232</t>
         </is>
       </c>
       <c r="K26" s="10">
-        <v>29.501489</v>
+        <v>29.59096</v>
       </c>
       <c r="L26" s="10">
-        <v>-98.702068</v>
+        <v>-98.47427</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -2659,15 +2803,15 @@
         </is>
       </c>
       <c r="U26" s="4">
-        <v>279692</v>
+        <v>295296</v>
       </c>
       <c r="V26" s="8">
-        <v>5500</v>
+        <v>3312.5</v>
       </c>
       <c r="W26" s="8"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="Z26" s="12" t="inlineStr">
         <is>
@@ -2682,7 +2826,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">005606</t>
+          <t xml:space="preserve">010208</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -2690,8 +2834,16 @@
           <t xml:space="preserve">Clear Channel Outdoor</t>
         </is>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samantha Idler</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -2699,17 +2851,17 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321953</t>
+          <t xml:space="preserve">30716116</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Potranco NS 0.2mi W/O W Military F/E - 2</t>
+          <t xml:space="preserve">Loop1604 SS .2miles E/O Stone Oak Pkwy F/E</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -2719,23 +2871,23 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78251</t>
+          <t xml:space="preserve">78232</t>
         </is>
       </c>
       <c r="K27" s="11">
-        <v>29.449667</v>
+        <v>29.608375</v>
       </c>
       <c r="L27" s="11">
-        <v>-98.647585</v>
+        <v>-98.48935</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -2750,7 +2902,7 @@
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="7">
-        <v>46286</v>
+        <v>46258</v>
       </c>
       <c r="S27" s="7">
         <v>46327</v>
@@ -2761,15 +2913,15 @@
         </is>
       </c>
       <c r="U27" s="5">
-        <v>159466</v>
+        <v>321050</v>
       </c>
       <c r="V27" s="9">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="W27" s="9"/>
       <c r="X27" s="5"/>
       <c r="Y27" s="5">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" s="13" t="inlineStr">
         <is>
@@ -2784,7 +2936,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">010206</t>
+          <t xml:space="preserve">010228</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2794,12 +2946,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2814,33 +2966,33 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30706737</t>
+          <t xml:space="preserve">30910116</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">US281 N WS 700ft S/O Thousand Oaks F/N</t>
+          <t xml:space="preserve">Loop 410 SS 150ft W/O West Ave F/W - 2</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hollywood park</t>
+          <t xml:space="preserve">San Antonio</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78232</t>
+          <t xml:space="preserve">78213</t>
         </is>
       </c>
       <c r="K28" s="10">
-        <v>29.59096</v>
+        <v>29.516444</v>
       </c>
       <c r="L28" s="10">
-        <v>-98.47427</v>
+        <v>-98.526629</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2871,7 +3023,7 @@
         </is>
       </c>
       <c r="U28" s="4">
-        <v>295296</v>
+        <v>900124</v>
       </c>
       <c r="V28" s="8">
         <v>3312.5</v>
@@ -2879,7 +3031,7 @@
       <c r="W28" s="8"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="inlineStr">
         <is>
@@ -2894,7 +3046,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">010208</t>
+          <t xml:space="preserve">010244</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -2904,12 +3056,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2919,48 +3071,48 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Digital</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30716116</t>
+          <t xml:space="preserve">30984505</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop1604 SS .2miles E/O Stone Oak Pkwy F/E</t>
+          <t xml:space="preserve">Hwy 78 SS 1.25mi E/O Loop 410 S F/SW - 2</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Kirby</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78232</t>
+          <t xml:space="preserve">78219</t>
         </is>
       </c>
       <c r="K29" s="11">
-        <v>29.608375</v>
+        <v>29.470937</v>
       </c>
       <c r="L29" s="11">
-        <v>-98.48935</v>
+        <v>-98.386922</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">SW</t>
         </is>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">10'6" x 36'</t>
         </is>
       </c>
       <c r="P29" s="5" t="inlineStr">
@@ -2981,15 +3133,15 @@
         </is>
       </c>
       <c r="U29" s="5">
-        <v>321050</v>
+        <v>44059</v>
       </c>
       <c r="V29" s="9">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="W29" s="9"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="5">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" s="13" t="inlineStr">
         <is>
@@ -3004,7 +3156,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">010228</t>
+          <t xml:space="preserve">010244</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -3014,12 +3166,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3034,33 +3186,33 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30910116</t>
+          <t xml:space="preserve">30984505</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 410 SS 150ft W/O West Ave F/W - 2</t>
+          <t xml:space="preserve">Hwy 78 SS 1.25mi E/O Loop 410 S F/SW - 2</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Kirby</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78213</t>
+          <t xml:space="preserve">78219</t>
         </is>
       </c>
       <c r="K30" s="10">
-        <v>29.516444</v>
+        <v>29.470937</v>
       </c>
       <c r="L30" s="10">
-        <v>-98.526629</v>
+        <v>-98.386922</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">SW</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
@@ -3070,7 +3222,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">10'6" x 36'</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -3091,15 +3243,15 @@
         </is>
       </c>
       <c r="U30" s="4">
-        <v>900124</v>
+        <v>44059</v>
       </c>
       <c r="V30" s="8">
-        <v>3312.5</v>
+        <v>800</v>
       </c>
       <c r="W30" s="8"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z30" s="12" t="inlineStr">
         <is>
@@ -3114,7 +3266,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">010244</t>
+          <t xml:space="preserve">10201</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3124,12 +3276,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stephanie Roach</t>
+          <t xml:space="preserve">Samantha Idler</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stephanieroach@clearchannel.com</t>
+          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3139,92 +3291,80 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30984505</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Digital Bulletin</t>
+        </is>
+      </c>
+      <c r="G31" s="5"/>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 78 SS 1.25mi E/O Loop 410 S F/SW - 2</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kirby</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78219</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Loop 1604 E .7Mi S/O Highway 78 F/N</t>
+        </is>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
       <c r="K31" s="11">
-        <v>29.470937</v>
+        <v>29.524347</v>
       </c>
       <c r="L31" s="11">
-        <v>-98.386922</v>
+        <v>-98.295924</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N31" s="5"/>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10'6" x 36'</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q31" s="5"/>
+          <t xml:space="preserve">14'' x 48''</t>
+        </is>
+      </c>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SA53 GO</t>
+        </is>
+      </c>
       <c r="R31" s="7">
-        <v>46258</v>
+        <v>46307</v>
       </c>
       <c r="S31" s="7">
-        <v>46327</v>
+        <v>46355</v>
       </c>
       <c r="T31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CCO 1307869-NSG HEB SAT 28 boards FULLY EXECUTED 8-13-26 (Sowrey 8-12, Carfagnini 8-13).pdf</t>
+          <t xml:space="preserve">HEB San Antonio 53 GO_encrypted_.pdf</t>
         </is>
       </c>
       <c r="U31" s="5">
-        <v>44059</v>
+        <v>65969</v>
       </c>
       <c r="V31" s="9">
-        <v>800</v>
+        <v>1335</v>
       </c>
       <c r="W31" s="9"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="Z31" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA31" s="5"/>
+        <v>4.6</v>
+      </c>
+      <c r="Z31" s="5"/>
+      <c r="AA31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Coming Soon</t>
+        </is>
+      </c>
       <c r="AB31" s="5"/>
       <c r="AC31" s="7"/>
-      <c r="AD31" s="5"/>
+      <c r="AD31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GO: Date Reveal</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10201</t>
+          <t xml:space="preserve">2569</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3249,80 +3389,84 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
-        </is>
-      </c>
-      <c r="G32" s="4"/>
+          <t xml:space="preserve">Static Premier Panel</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">319526</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 1604 E .7Mi S/O Highway 78 F/N</t>
+          <t xml:space="preserve">Fredericksburg 15 ft S/ O West Av ES</t>
         </is>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="10">
-        <v>29.524347</v>
+        <v>29.4646</v>
       </c>
       <c r="L32" s="10">
-        <v>-98.295924</v>
+        <v>-98.5258</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">Southeast</t>
         </is>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">12'3" x 24'6"</t>
         </is>
       </c>
       <c r="P32" s="4"/>
       <c r="Q32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SA53 GO</t>
+          <t xml:space="preserve">PLA</t>
         </is>
       </c>
       <c r="R32" s="6">
-        <v>46307</v>
+        <v>45962</v>
       </c>
       <c r="S32" s="6">
-        <v>46355</v>
+        <v>47787</v>
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB San Antonio 53 GO_encrypted_.pdf</t>
+          <t xml:space="preserve">CCO_HEB Lease Agrmnt 7279 Fres_West Ave 2026 - signed (002).pdf</t>
         </is>
       </c>
       <c r="U32" s="4">
-        <v>65969</v>
+        <v>29195</v>
       </c>
       <c r="V32" s="8">
-        <v>1335</v>
+        <v>0</v>
       </c>
       <c r="W32" s="8"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Coming Soon</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB32" s="4"/>
       <c r="AC32" s="6"/>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Date Reveal</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569</t>
+          <t xml:space="preserve">3428</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3347,36 +3491,36 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Premier Panel</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">319526</t>
+          <t xml:space="preserve">319948</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fredericksburg 15 ft S/ O West Av ES</t>
+          <t xml:space="preserve">West Ave 100' S/O Blanco WS</t>
         </is>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="11">
-        <v>29.4646</v>
+        <v>29.5463</v>
       </c>
       <c r="L33" s="11">
-        <v>-98.5258</v>
+        <v>-98.5093</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southeast</t>
+          <t xml:space="preserve">Southwest</t>
         </is>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'3" x 24'6"</t>
+          <t xml:space="preserve">10.5' x 36'</t>
         </is>
       </c>
       <c r="P33" s="5"/>
@@ -3386,31 +3530,31 @@
         </is>
       </c>
       <c r="R33" s="7">
-        <v>45962</v>
+        <v>46209</v>
       </c>
       <c r="S33" s="7">
-        <v>47787</v>
-      </c>
-      <c r="T33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CCO_HEB Lease Agrmnt 7279 Fres_West Ave 2026 - signed (002).pdf</t>
-        </is>
-      </c>
+        <v>46474</v>
+      </c>
+      <c r="T33" s="5"/>
       <c r="U33" s="5">
-        <v>29195</v>
+        <v>84337</v>
       </c>
       <c r="V33" s="9">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="W33" s="9"/>
       <c r="X33" s="5"/>
       <c r="Y33" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="Z33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB33" s="5"/>
@@ -3424,7 +3568,7 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3428</t>
+          <t xml:space="preserve">4126</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3449,30 +3593,30 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">319948</t>
+          <t xml:space="preserve">320512</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West Ave 100' S/O Blanco WS</t>
+          <t xml:space="preserve">1604 &amp; Bandera</t>
         </is>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="10">
-        <v>29.5463</v>
+        <v>29.55379682</v>
       </c>
       <c r="L34" s="10">
-        <v>-98.5093</v>
+        <v>-98.66566211</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southwest</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N34" s="4"/>
@@ -3488,22 +3632,26 @@
         </is>
       </c>
       <c r="R34" s="6">
-        <v>46209</v>
+        <v>46125</v>
       </c>
       <c r="S34" s="6">
-        <v>46474</v>
-      </c>
-      <c r="T34" s="4"/>
+        <v>46488</v>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CCO_HEB Lease Agrmnt 2026 cco sgnd.pdf</t>
+        </is>
+      </c>
       <c r="U34" s="4">
-        <v>84337</v>
+        <v>86239</v>
       </c>
       <c r="V34" s="8">
-        <v>1465</v>
+        <v>0</v>
       </c>
       <c r="W34" s="8"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="Z34" s="12" t="inlineStr">
         <is>
@@ -3526,7 +3674,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126</t>
+          <t xml:space="preserve">4338</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3551,36 +3699,36 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">320512</t>
+          <t xml:space="preserve">320803</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1604 &amp; Bandera</t>
+          <t xml:space="preserve">I-10 NW 100ft n/o DeZavala ES</t>
         </is>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="11">
-        <v>29.55379682</v>
+        <v>29.5639</v>
       </c>
       <c r="L35" s="11">
-        <v>-98.66566211</v>
+        <v>-98.5903</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.5' x 36'</t>
+          <t xml:space="preserve">20' x 60'</t>
         </is>
       </c>
       <c r="P35" s="5"/>
@@ -3590,21 +3738,17 @@
         </is>
       </c>
       <c r="R35" s="7">
-        <v>46125</v>
+        <v>46209</v>
       </c>
       <c r="S35" s="7">
-        <v>46488</v>
-      </c>
-      <c r="T35" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CCO_HEB Lease Agrmnt 2026 cco sgnd.pdf</t>
-        </is>
-      </c>
+        <v>46439</v>
+      </c>
+      <c r="T35" s="5"/>
       <c r="U35" s="5">
-        <v>86239</v>
+        <v>601051</v>
       </c>
       <c r="V35" s="9">
-        <v>0</v>
+        <v>7875</v>
       </c>
       <c r="W35" s="9"/>
       <c r="X35" s="5"/>
@@ -3632,7 +3776,7 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4338</t>
+          <t xml:space="preserve">4446</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -3662,31 +3806,31 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">320803</t>
+          <t xml:space="preserve">321003</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-10 NW 100ft n/o DeZavala ES</t>
+          <t xml:space="preserve">West Ave 100' W/O Blanco NS</t>
         </is>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="10">
-        <v>29.5639</v>
+        <v>29.5462</v>
       </c>
       <c r="L36" s="10">
-        <v>-98.5903</v>
+        <v>-98.5093</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N36" s="4"/>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">20' x 60'</t>
+          <t xml:space="preserve">10.5' x 36'</t>
         </is>
       </c>
       <c r="P36" s="4"/>
@@ -3699,19 +3843,19 @@
         <v>46209</v>
       </c>
       <c r="S36" s="6">
-        <v>46439</v>
+        <v>46292</v>
       </c>
       <c r="T36" s="4"/>
       <c r="U36" s="4">
-        <v>601051</v>
+        <v>234667</v>
       </c>
       <c r="V36" s="8">
-        <v>7875</v>
+        <v>1775</v>
       </c>
       <c r="W36" s="8"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Z36" s="12" t="inlineStr">
         <is>
@@ -3720,7 +3864,7 @@
       </c>
       <c r="AA36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB36" s="4"/>
@@ -3734,22 +3878,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4446</t>
+          <t xml:space="preserve">54</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clear Channel Outdoor</t>
+          <t xml:space="preserve">Gunnarson Outdoor Advertising</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samantha Idler</t>
+          <t xml:space="preserve">Jason Cragg</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+          <t xml:space="preserve">billboards@gunnarsonadvertising.com</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -3762,81 +3906,81 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321003</t>
-        </is>
-      </c>
+      <c r="G37" s="5"/>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West Ave 100' W/O Blanco NS</t>
-        </is>
-      </c>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
+          <t xml:space="preserve">IH-35,Near Walnut Avenue</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Braunfels</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78130</t>
+        </is>
+      </c>
       <c r="K37" s="11">
-        <v>29.5462</v>
+        <v>29.69</v>
       </c>
       <c r="L37" s="11">
-        <v>-98.5093</v>
+        <v>-98.13</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
-        </is>
-      </c>
-      <c r="N37" s="5"/>
+          <t xml:space="preserve">N</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10.5' x 36'</t>
-        </is>
-      </c>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q37" s="5"/>
       <c r="R37" s="7">
-        <v>46209</v>
+        <v>46266</v>
       </c>
       <c r="S37" s="7">
-        <v>46292</v>
-      </c>
-      <c r="T37" s="5"/>
+        <v>46326</v>
+      </c>
+      <c r="T37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gunnarson 54RH 62RH 74CR leases 21650 PARTIAL 8-12-26 (74CR NOT HEB-signed; all 3 awaiting Gunnarson).pdf</t>
+        </is>
+      </c>
       <c r="U37" s="5">
-        <v>234667</v>
+        <v>450000</v>
       </c>
       <c r="V37" s="9">
-        <v>1775</v>
+        <v>4275</v>
       </c>
       <c r="W37" s="9"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Z37" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We have marinated meats</t>
-        </is>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="Z37" s="5"/>
+      <c r="AA37" s="5"/>
       <c r="AB37" s="5"/>
       <c r="AC37" s="7"/>
-      <c r="AD37" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
-        </is>
-      </c>
+      <c r="AD37" s="5"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">54</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -3844,8 +3988,16 @@
           <t xml:space="preserve">Gunnarson Outdoor Advertising</t>
         </is>
       </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jason Cragg</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">billboards@gunnarsonadvertising.com</t>
+        </is>
+      </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -3859,28 +4011,28 @@
       <c r="G38" s="4"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35,Near Walnut Avenue</t>
+          <t xml:space="preserve">IH-35, South of Hwy 3009</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Braunfels</t>
+          <t xml:space="preserve">Schertz</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78130</t>
+          <t xml:space="preserve">78154</t>
         </is>
       </c>
       <c r="K38" s="10">
-        <v>29.69</v>
+        <v>29.6</v>
       </c>
       <c r="L38" s="10">
-        <v>-98.13</v>
+        <v>-98.28</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
+          <t xml:space="preserve">S</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -3890,7 +4042,7 @@
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">12' x 40'</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
@@ -3911,15 +4063,15 @@
         </is>
       </c>
       <c r="U38" s="4">
-        <v>450000</v>
+        <v>420000</v>
       </c>
       <c r="V38" s="8">
-        <v>4275</v>
+        <v>3275</v>
       </c>
       <c r="W38" s="8"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
@@ -3930,7 +4082,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">74</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3938,8 +4090,16 @@
           <t xml:space="preserve">Gunnarson Outdoor Advertising</t>
         </is>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jason Cragg</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">billboards@gunnarsonadvertising.com</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -3953,33 +4113,33 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35, South of Hwy 3009</t>
+          <t xml:space="preserve">IH-35,1/2 mile south of Hwy 306</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schertz</t>
+          <t xml:space="preserve">New Braunfels</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78154</t>
+          <t xml:space="preserve">78130</t>
         </is>
       </c>
       <c r="K39" s="11">
-        <v>29.6</v>
+        <v>29.72</v>
       </c>
       <c r="L39" s="11">
-        <v>-98.28</v>
+        <v>-98.09</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S</t>
+          <t xml:space="preserve">N</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -4005,7 +4165,7 @@
         </is>
       </c>
       <c r="U39" s="5">
-        <v>420000</v>
+        <v>400000</v>
       </c>
       <c r="V39" s="9">
         <v>3275</v>
@@ -4013,7 +4173,7 @@
       <c r="W39" s="9"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="Z39" s="5"/>
       <c r="AA39" s="5"/>
@@ -4024,16 +4184,24 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">74</t>
+          <t xml:space="preserve">East Face</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunnarson Outdoor Advertising</t>
-        </is>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
+          <t xml:space="preserve">Keller Custom Signs</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corey (Keller Billboard Sales)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corey@kellercustomsigns.com</t>
+        </is>
+      </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -4047,69 +4215,55 @@
       <c r="G40" s="4"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-35,1/2 mile south of Hwy 306</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New Braunfels</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78130</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Double Sided Board (Colonnade) **10-year addendum effective 4/1/21** Total cost reflects PER year</t>
+        </is>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
       <c r="K40" s="10">
-        <v>29.72</v>
+        <v>29.530394</v>
       </c>
       <c r="L40" s="10">
-        <v>-98.09</v>
+        <v>-98.560385</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N</t>
-        </is>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CR</t>
-        </is>
-      </c>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N40" s="4"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' x 40'</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
       <c r="R40" s="6">
-        <v>46266</v>
+        <v>46209</v>
       </c>
       <c r="S40" s="6">
-        <v>46326</v>
+        <v>47938</v>
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gunnarson 54RH 62RH 74CR leases 21650 PARTIAL 8-12-26 (74CR NOT HEB-signed; all 3 awaiting Gunnarson).pdf</t>
-        </is>
-      </c>
-      <c r="U40" s="4">
-        <v>400000</v>
-      </c>
+          <t xml:space="preserve">Keller contract copy.pdf</t>
+        </is>
+      </c>
+      <c r="U40" s="4"/>
       <c r="V40" s="8">
-        <v>3275</v>
+        <v>5566</v>
       </c>
       <c r="W40" s="8"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4">
-        <v>3.1</v>
-      </c>
-      <c r="Z40" s="4"/>
+        <v>2.2</v>
+      </c>
+      <c r="Z40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA40" s="4"/>
       <c r="AB40" s="4"/>
       <c r="AC40" s="6"/>
@@ -4118,7 +4272,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East Face</t>
+          <t xml:space="preserve">West Face</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -4126,7 +4280,11 @@
           <t xml:space="preserve">Keller Custom Signs</t>
         </is>
       </c>
-      <c r="C41" s="5"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corey (Keller Billboard Sales)</t>
+        </is>
+      </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Corey@kellercustomsigns.com</t>
@@ -4158,7 +4316,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N41" s="5"/>
@@ -4187,7 +4345,7 @@
       <c r="W41" s="9"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="Z41" s="13" t="inlineStr">
         <is>
@@ -4202,18 +4360,22 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West Face</t>
+          <t xml:space="preserve">TX305S</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keller Custom Signs</t>
-        </is>
-      </c>
-      <c r="C42" s="4"/>
+          <t xml:space="preserve">Kenjoh Outdoor</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jake (Kenjoh)</t>
+        </is>
+      </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corey@kellercustomsigns.com</t>
+          <t xml:space="preserve">jake@kenjohoutdoor.com</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -4223,55 +4385,65 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
-        </is>
-      </c>
-      <c r="G42" s="4"/>
+          <t xml:space="preserve">Digital Bulletin</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50815970</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Double Sided Board (Colonnade) **10-year addendum effective 4/1/21** Total cost reflects PER year</t>
-        </is>
-      </c>
-      <c r="I42" s="4"/>
+          <t xml:space="preserve">Loop 1604 W/L .6 Miles South of I-35</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Live Oak</t>
+        </is>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="10">
-        <v>29.530394</v>
+        <v>29.56</v>
       </c>
       <c r="L42" s="10">
-        <v>-98.560385</v>
+        <v>-98.327528</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">11' x 36'</t>
         </is>
       </c>
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="6">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="S42" s="6">
-        <v>47938</v>
+        <v>46327</v>
       </c>
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keller contract copy.pdf</t>
-        </is>
-      </c>
-      <c r="U42" s="4"/>
+          <t xml:space="preserve">Kenjoh 3902-1 TX305S.1 TX309W.1 HEB-SIGNED 8-12-26 (awaiting Kenjoh GM).pdf</t>
+        </is>
+      </c>
+      <c r="U42" s="4">
+        <v>68098</v>
+      </c>
       <c r="V42" s="8">
-        <v>5566</v>
+        <v>1250</v>
       </c>
       <c r="W42" s="8"/>
       <c r="X42" s="4"/>
       <c r="Y42" s="4">
-        <v>0.2</v>
+        <v>3.7</v>
       </c>
       <c r="Z42" s="12" t="inlineStr">
         <is>
@@ -4286,7 +4458,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX305S</t>
+          <t xml:space="preserve">TX309W</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4311,49 +4483,53 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50815970</t>
+          <t xml:space="preserve">50801563</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loop 1604 W/L .6 Miles South of I-35</t>
+          <t xml:space="preserve">West Avenue W/L at Jackson Keller Rd, West Face</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live Oak</t>
+          <t xml:space="preserve">San Antonio</t>
         </is>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="11">
-        <v>29.56</v>
+        <v>29.515291</v>
       </c>
       <c r="L43" s="11">
-        <v>-98.327528</v>
+        <v>-98.526158</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">11' x 36'</t>
-        </is>
-      </c>
-      <c r="P43" s="5"/>
+          <t xml:space="preserve">10' x 30'</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="7">
         <v>46258</v>
       </c>
       <c r="S43" s="7">
-        <v>46327</v>
+        <v>46621</v>
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
@@ -4361,15 +4537,15 @@
         </is>
       </c>
       <c r="U43" s="5">
-        <v>68098</v>
+        <v>80734</v>
       </c>
       <c r="V43" s="9">
-        <v>1250</v>
+        <v>2400</v>
       </c>
       <c r="W43" s="9"/>
       <c r="X43" s="5"/>
       <c r="Y43" s="5">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="Z43" s="13" t="inlineStr">
         <is>
@@ -4384,22 +4560,22 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX309W</t>
+          <t xml:space="preserve">1344</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenjoh Outdoor</t>
+          <t xml:space="preserve">Lamar Advertising</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jake (Kenjoh)</t>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jake@kenjohoutdoor.com</t>
+          <t xml:space="preserve">boconnor@lamar.com</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -4409,40 +4585,48 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">50801563</t>
+          <t xml:space="preserve">155022</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West Avenue W/L at Jackson Keller Rd, West Face</t>
+          <t xml:space="preserve">N/S I-10 1.8 MI E/O LOOP 1604</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
-        </is>
-      </c>
-      <c r="J44" s="4"/>
+          <t xml:space="preserve">Schertz</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78154</t>
+        </is>
+      </c>
       <c r="K44" s="10">
-        <v>29.515291</v>
+        <v>29.48</v>
       </c>
       <c r="L44" s="10">
-        <v>-98.526158</v>
+        <v>-98.26</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N44" s="4"/>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' x 30'</t>
+          <t xml:space="preserve">10' 0" x 40' 0"</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
@@ -4455,29 +4639,25 @@
         <v>46258</v>
       </c>
       <c r="S44" s="6">
-        <v>46621</v>
+        <v>46341</v>
       </c>
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kenjoh 3902-1 TX305S.1 TX309W.1 HEB-SIGNED 8-12-26 (awaiting Kenjoh GM).pdf</t>
+          <t xml:space="preserve">Lamar C5686691 REV2 SA DMA 10 boards HEB-SIGNED 8-12-26 (awaiting Lamar GM).pdf</t>
         </is>
       </c>
       <c r="U44" s="4">
-        <v>80734</v>
+        <v>169587</v>
       </c>
       <c r="V44" s="8">
-        <v>2400</v>
+        <v>2250</v>
       </c>
       <c r="W44" s="8"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="Z44" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
       <c r="AB44" s="4"/>
       <c r="AC44" s="6"/>
@@ -4486,7 +4666,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344</t>
+          <t xml:space="preserve">1352</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4494,8 +4674,16 @@
           <t xml:space="preserve">Lamar Advertising</t>
         </is>
       </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boconnor@lamar.com</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -4508,43 +4696,43 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">155022</t>
+          <t xml:space="preserve">155030</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/S I-10 1.8 MI E/O LOOP 1604</t>
+          <t xml:space="preserve">IH-10 W., 4/10 MI E/O MM 545</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schertz</t>
+          <t xml:space="preserve">Boerne</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78154</t>
+          <t xml:space="preserve">78006</t>
         </is>
       </c>
       <c r="K45" s="11">
-        <v>29.48</v>
+        <v>29.7341</v>
       </c>
       <c r="L45" s="11">
-        <v>-98.26</v>
+        <v>-98.683</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">South East</t>
         </is>
       </c>
       <c r="N45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' 0" x 40' 0"</t>
+          <t xml:space="preserve">14' 0" x 48' 0"</t>
         </is>
       </c>
       <c r="P45" s="5" t="inlineStr">
@@ -4565,17 +4753,21 @@
         </is>
       </c>
       <c r="U45" s="5">
-        <v>169587</v>
+        <v>255759</v>
       </c>
       <c r="V45" s="9">
-        <v>2250</v>
+        <v>4050</v>
       </c>
       <c r="W45" s="9"/>
       <c r="X45" s="5"/>
       <c r="Y45" s="5">
-        <v>5.7</v>
-      </c>
-      <c r="Z45" s="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="Z45" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA45" s="5"/>
       <c r="AB45" s="5"/>
       <c r="AC45" s="7"/>
@@ -4584,7 +4776,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352</t>
+          <t xml:space="preserve">1353</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4614,29 +4806,29 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">155030</t>
+          <t xml:space="preserve">155031</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">IH-10 W., 4/10 MI E/O MM 545</t>
+          <t xml:space="preserve">N/S BANDERA RD. 3.8 MI E/O LP 1604</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boerne</t>
+          <t xml:space="preserve">San Antonio</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78006</t>
+          <t xml:space="preserve">78238</t>
         </is>
       </c>
       <c r="K46" s="10">
-        <v>29.7341</v>
+        <v>29.5095</v>
       </c>
       <c r="L46" s="10">
-        <v>-98.683</v>
+        <v>-98.6299</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -4645,12 +4837,12 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' 0" x 48' 0"</t>
+          <t xml:space="preserve">10' 6" x 40' 0"</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
@@ -4671,15 +4863,15 @@
         </is>
       </c>
       <c r="U46" s="4">
-        <v>255759</v>
+        <v>406505</v>
       </c>
       <c r="V46" s="8">
-        <v>4050</v>
+        <v>2700</v>
       </c>
       <c r="W46" s="8"/>
       <c r="X46" s="4"/>
       <c r="Y46" s="4">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="Z46" s="12" t="inlineStr">
         <is>
@@ -4694,7 +4886,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1353</t>
+          <t xml:space="preserve">1680</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4724,12 +4916,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">155031</t>
+          <t xml:space="preserve">155304</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/S BANDERA RD. 3.8 MI E/O LP 1604</t>
+          <t xml:space="preserve">LOOP 1604 @ POTRANCO RD.</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -4739,28 +4931,28 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78238</t>
+          <t xml:space="preserve">78253</t>
         </is>
       </c>
       <c r="K47" s="11">
-        <v>29.5095</v>
+        <v>29.4376</v>
       </c>
       <c r="L47" s="11">
-        <v>-98.6299</v>
+        <v>-98.7123</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South East</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' 6" x 40' 0"</t>
+          <t xml:space="preserve">14' 0" x 48' 0"</t>
         </is>
       </c>
       <c r="P47" s="5" t="inlineStr">
@@ -4770,10 +4962,10 @@
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="7">
-        <v>46258</v>
+        <v>46293</v>
       </c>
       <c r="S47" s="7">
-        <v>46341</v>
+        <v>46376</v>
       </c>
       <c r="T47" s="5" t="inlineStr">
         <is>
@@ -4781,15 +4973,15 @@
         </is>
       </c>
       <c r="U47" s="5">
-        <v>406505</v>
+        <v>62485</v>
       </c>
       <c r="V47" s="9">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="W47" s="9"/>
       <c r="X47" s="5"/>
       <c r="Y47" s="5">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z47" s="13" t="inlineStr">
         <is>
@@ -4804,7 +4996,7 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680</t>
+          <t xml:space="preserve">40021</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4834,12 +5026,12 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">155304</t>
+          <t xml:space="preserve">618175</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOOP 1604 @ POTRANCO RD.</t>
+          <t xml:space="preserve">E/S I-10 500' N/O Hildebrand</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -4849,18 +5041,18 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78253</t>
+          <t xml:space="preserve">78201</t>
         </is>
       </c>
       <c r="K48" s="10">
-        <v>29.4376</v>
+        <v>29.469</v>
       </c>
       <c r="L48" s="10">
-        <v>-98.7123</v>
+        <v>-98.5153</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -4891,7 +5083,7 @@
         </is>
       </c>
       <c r="U48" s="4">
-        <v>62485</v>
+        <v>849571</v>
       </c>
       <c r="V48" s="8">
         <v>3600</v>
@@ -4899,7 +5091,7 @@
       <c r="W48" s="8"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Z48" s="12" t="inlineStr">
         <is>
@@ -4914,7 +5106,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">40021</t>
+          <t xml:space="preserve">40081</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -4944,12 +5136,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">618175</t>
+          <t xml:space="preserve">618187</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S I-10 500' N/O Hildebrand</t>
+          <t xml:space="preserve">E/S 281 1000' N/O EVANS RD.</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -4959,14 +5151,14 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78201</t>
+          <t xml:space="preserve">78259</t>
         </is>
       </c>
       <c r="K49" s="11">
-        <v>29.469</v>
+        <v>29.64</v>
       </c>
       <c r="L49" s="11">
-        <v>-98.5153</v>
+        <v>-98.45</v>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
@@ -5001,7 +5193,7 @@
         </is>
       </c>
       <c r="U49" s="5">
-        <v>849571</v>
+        <v>274454</v>
       </c>
       <c r="V49" s="9">
         <v>3600</v>
@@ -5009,13 +5201,9 @@
       <c r="W49" s="9"/>
       <c r="X49" s="5"/>
       <c r="Y49" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="Z49" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
       <c r="AB49" s="5"/>
       <c r="AC49" s="7"/>
@@ -5024,7 +5212,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40081</t>
+          <t xml:space="preserve">40111</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -5032,8 +5220,16 @@
           <t xml:space="preserve">Lamar Advertising</t>
         </is>
       </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boconnor@lamar.com</t>
+        </is>
+      </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -5046,12 +5242,12 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">618187</t>
+          <t xml:space="preserve">618192</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S 281 1000' N/O EVANS RD.</t>
+          <t xml:space="preserve">I-10-W/S @ BALCONES RD.</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -5061,18 +5257,18 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78259</t>
+          <t xml:space="preserve">78201</t>
         </is>
       </c>
       <c r="K50" s="10">
-        <v>29.64</v>
+        <v>29.4884</v>
       </c>
       <c r="L50" s="10">
-        <v>-98.45</v>
+        <v>-98.546</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South East</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -5092,10 +5288,10 @@
       </c>
       <c r="Q50" s="4"/>
       <c r="R50" s="6">
-        <v>46293</v>
+        <v>46258</v>
       </c>
       <c r="S50" s="6">
-        <v>46376</v>
+        <v>46341</v>
       </c>
       <c r="T50" s="4" t="inlineStr">
         <is>
@@ -5103,7 +5299,7 @@
         </is>
       </c>
       <c r="U50" s="4">
-        <v>274454</v>
+        <v>723436</v>
       </c>
       <c r="V50" s="8">
         <v>3600</v>
@@ -5111,9 +5307,13 @@
       <c r="W50" s="8"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="Z50" s="4"/>
+        <v>2.1</v>
+      </c>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA50" s="4"/>
       <c r="AB50" s="4"/>
       <c r="AC50" s="6"/>
@@ -5122,7 +5322,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">40111</t>
+          <t xml:space="preserve">40182</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -5147,17 +5347,17 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">618192</t>
+          <t xml:space="preserve">30497070</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-10-W/S @ BALCONES RD.</t>
+          <t xml:space="preserve">E/S 281 1000'N/O EVANS RD.F/S</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -5167,23 +5367,23 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78201</t>
+          <t xml:space="preserve">78259</t>
         </is>
       </c>
       <c r="K51" s="11">
-        <v>29.4884</v>
+        <v>29.6403</v>
       </c>
       <c r="L51" s="11">
-        <v>-98.546</v>
+        <v>-98.4538</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South East</t>
+          <t xml:space="preserve">South West</t>
         </is>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -5209,7 +5409,7 @@
         </is>
       </c>
       <c r="U51" s="5">
-        <v>723436</v>
+        <v>314740</v>
       </c>
       <c r="V51" s="9">
         <v>3600</v>
@@ -5217,7 +5417,7 @@
       <c r="W51" s="9"/>
       <c r="X51" s="5"/>
       <c r="Y51" s="5">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z51" s="13" t="inlineStr">
         <is>
@@ -5232,7 +5432,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">40182</t>
+          <t xml:space="preserve">44531</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -5257,48 +5457,48 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30497070</t>
+          <t xml:space="preserve">30663396</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/S 281 1000'N/O EVANS RD.F/S</t>
+          <t xml:space="preserve">S/SI-10 1.9 MI E/O SR 46</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Boerne</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78259</t>
+          <t xml:space="preserve">78006</t>
         </is>
       </c>
       <c r="K52" s="10">
-        <v>29.6403</v>
+        <v>29.76</v>
       </c>
       <c r="L52" s="10">
-        <v>-98.4538</v>
+        <v>-98.71</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South West</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' 0" x 48' 0"</t>
+          <t xml:space="preserve">10' 0" x 40' 0"</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
@@ -5308,10 +5508,10 @@
       </c>
       <c r="Q52" s="4"/>
       <c r="R52" s="6">
-        <v>46258</v>
+        <v>46314</v>
       </c>
       <c r="S52" s="6">
-        <v>46341</v>
+        <v>46397</v>
       </c>
       <c r="T52" s="4" t="inlineStr">
         <is>
@@ -5319,21 +5519,17 @@
         </is>
       </c>
       <c r="U52" s="4">
-        <v>314740</v>
+        <v>296736</v>
       </c>
       <c r="V52" s="8">
-        <v>3600</v>
+        <v>3150</v>
       </c>
       <c r="W52" s="8"/>
       <c r="X52" s="4"/>
       <c r="Y52" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="Z52" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
       <c r="AB52" s="4"/>
       <c r="AC52" s="6"/>
@@ -5342,7 +5538,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">44531</t>
+          <t xml:space="preserve">90391</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
@@ -5350,8 +5546,16 @@
           <t xml:space="preserve">Lamar Advertising</t>
         </is>
       </c>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boconnor@lamar.com</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -5364,33 +5568,33 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30663396</t>
+          <t xml:space="preserve">155742</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">S/SI-10 1.9 MI E/O SR 46</t>
+          <t xml:space="preserve">W/S I-35 S/O LOOP 337</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boerne</t>
+          <t xml:space="preserve">New Braunfels</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78006</t>
+          <t xml:space="preserve">78132</t>
         </is>
       </c>
       <c r="K53" s="11">
-        <v>29.76</v>
+        <v>29.67</v>
       </c>
       <c r="L53" s="11">
-        <v>-98.71</v>
+        <v>-98.16</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">South West</t>
         </is>
       </c>
       <c r="N53" s="5" t="inlineStr">
@@ -5400,7 +5604,7 @@
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' 0" x 40' 0"</t>
+          <t xml:space="preserve">14' 0" x 48' 0"</t>
         </is>
       </c>
       <c r="P53" s="5" t="inlineStr">
@@ -5410,10 +5614,10 @@
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="7">
-        <v>46314</v>
+        <v>46265</v>
       </c>
       <c r="S53" s="7">
-        <v>46397</v>
+        <v>46320</v>
       </c>
       <c r="T53" s="5" t="inlineStr">
         <is>
@@ -5421,15 +5625,15 @@
         </is>
       </c>
       <c r="U53" s="5">
-        <v>296736</v>
+        <v>461327</v>
       </c>
       <c r="V53" s="9">
-        <v>3150</v>
+        <v>4050</v>
       </c>
       <c r="W53" s="9"/>
       <c r="X53" s="5"/>
       <c r="Y53" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z53" s="5"/>
       <c r="AA53" s="5"/>
@@ -5440,16 +5644,24 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">90391</t>
+          <t xml:space="preserve">Board 2</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Advertising</t>
-        </is>
-      </c>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
+          <t xml:space="preserve">Media Outdoor Displays</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audrey Poole</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audrey@mediaoutdoordisplays.com</t>
+        </is>
+      </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -5457,48 +5669,40 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155742</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Static Bulletin</t>
+        </is>
+      </c>
+      <c r="G54" s="4"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S I-35 S/O LOOP 337</t>
+          <t xml:space="preserve">ES IH-37, S/O Southcross - F/S (@ Gevers)</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Braunfels</t>
+          <t xml:space="preserve">San Antonio</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78132</t>
+          <t xml:space="preserve">78223</t>
         </is>
       </c>
       <c r="K54" s="10">
-        <v>29.67</v>
+        <v>29.373491</v>
       </c>
       <c r="L54" s="10">
-        <v>-98.16</v>
+        <v>-98.456268</v>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South West</t>
-        </is>
-      </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+          <t xml:space="preserve">South</t>
+        </is>
+      </c>
+      <c r="N54" s="4"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' 0" x 48' 0"</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
@@ -5508,28 +5712,30 @@
       </c>
       <c r="Q54" s="4"/>
       <c r="R54" s="6">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="S54" s="6">
-        <v>46320</v>
+        <v>46442</v>
       </c>
       <c r="T54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar C5686691 REV2 SA DMA 10 boards HEB-SIGNED 8-12-26 (awaiting Lamar GM).pdf</t>
-        </is>
-      </c>
-      <c r="U54" s="4">
-        <v>461327</v>
-      </c>
+          <t xml:space="preserve">MOD Board 2 + Board 6 SA EXECUTED 8-12-26 (both signed).pdf</t>
+        </is>
+      </c>
+      <c r="U54" s="4"/>
       <c r="V54" s="8">
-        <v>4050</v>
+        <v>1500</v>
       </c>
       <c r="W54" s="8"/>
       <c r="X54" s="4"/>
       <c r="Y54" s="4">
-        <v>1</v>
-      </c>
-      <c r="Z54" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA54" s="4"/>
       <c r="AB54" s="4"/>
       <c r="AC54" s="6"/>
@@ -5538,7 +5744,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board 2</t>
+          <t xml:space="preserve">Board 6 FN</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5569,34 +5775,34 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ES IH-37, S/O Southcross - F/S (@ Gevers)</t>
+          <t xml:space="preserve">ES I-10 W, S/O Old Fredericksburg Rd. - F/N</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Fair Oaks Ranch</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78223</t>
+          <t xml:space="preserve">78006</t>
         </is>
       </c>
       <c r="K55" s="11">
-        <v>29.373491</v>
+        <v>29.692365</v>
       </c>
       <c r="L55" s="11">
-        <v>-98.456268</v>
+        <v>-98.646394</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N55" s="5"/>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">12' x 36'</t>
         </is>
       </c>
       <c r="P55" s="5" t="inlineStr">
@@ -5609,7 +5815,7 @@
         <v>46259</v>
       </c>
       <c r="S55" s="7">
-        <v>46442</v>
+        <v>46623</v>
       </c>
       <c r="T55" s="5" t="inlineStr">
         <is>
@@ -5623,7 +5829,7 @@
       <c r="W55" s="9"/>
       <c r="X55" s="5"/>
       <c r="Y55" s="5">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="Z55" s="13" t="inlineStr">
         <is>
@@ -5638,22 +5844,22 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Board 6 FN</t>
+          <t xml:space="preserve">TX39A</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Media Outdoor Displays</t>
+          <t xml:space="preserve">MH Outdoor Media</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audrey Poole</t>
+          <t xml:space="preserve">Brandon Wilburn</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audrey@mediaoutdoordisplays.com</t>
+          <t xml:space="preserve">bwilburn@machaik.com</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -5663,40 +5869,44 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ES I-10 W, S/O Old Fredericksburg Rd. - F/N</t>
+          <t xml:space="preserve">N/S of IH-10 East, .7 Miles E/o Loop 1604.     Exit 587, E/F</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fair Oaks Ranch</t>
+          <t xml:space="preserve">San Antonio</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78006</t>
+          <t xml:space="preserve">78230</t>
         </is>
       </c>
       <c r="K56" s="10">
-        <v>29.692365</v>
+        <v>29.469312</v>
       </c>
       <c r="L56" s="10">
-        <v>-98.646394</v>
+        <v>-98.281866</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
-        </is>
-      </c>
-      <c r="N56" s="4"/>
+          <t xml:space="preserve">E/F</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12' x 36'</t>
+          <t xml:space="preserve">14'0x48'0</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -5706,30 +5916,28 @@
       </c>
       <c r="Q56" s="4"/>
       <c r="R56" s="6">
-        <v>46259</v>
+        <v>46398</v>
       </c>
       <c r="S56" s="6">
-        <v>46623</v>
+        <v>46761</v>
       </c>
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOD Board 2 + Board 6 SA EXECUTED 8-12-26 (both signed).pdf</t>
-        </is>
-      </c>
-      <c r="U56" s="4"/>
+          <t xml:space="preserve">MH Outdoor 15491-4 TX39A HEB-SIGNED 8-26-26 (awaiting MH signature).pdf</t>
+        </is>
+      </c>
+      <c r="U56" s="4">
+        <v>1536325</v>
+      </c>
       <c r="V56" s="8">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="W56" s="8"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="4">
-        <v>2.1</v>
-      </c>
-      <c r="Z56" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
       <c r="AB56" s="4"/>
       <c r="AC56" s="6"/>
@@ -5738,7 +5946,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX39A</t>
+          <t xml:space="preserve">TX46B</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5746,8 +5954,16 @@
           <t xml:space="preserve">MH Outdoor Media</t>
         </is>
       </c>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brandon Wilburn</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bwilburn@machaik.com</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">San Antonio</t>
@@ -5755,44 +5971,44 @@
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/S of IH-10 East, .7 Miles E/o Loop 1604.     Exit 587, E/F</t>
+          <t xml:space="preserve">N/S of Hwy 90 Bus., 600 feet E/o FM 725.    Seguin, Texas N/S, W/F</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">San Antonio</t>
+          <t xml:space="preserve">Seguin</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78230</t>
+          <t xml:space="preserve">78155</t>
         </is>
       </c>
       <c r="K57" s="11">
-        <v>29.469312</v>
+        <v>29.555712</v>
       </c>
       <c r="L57" s="11">
-        <v>-98.281866</v>
+        <v>-98.027557</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">E/F</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'0x48'0</t>
+          <t xml:space="preserve">10' x 30'</t>
         </is>
       </c>
       <c r="P57" s="5" t="inlineStr">
@@ -5802,28 +6018,32 @@
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="7">
-        <v>46398</v>
+        <v>46258</v>
       </c>
       <c r="S57" s="7">
-        <v>46761</v>
+        <v>46299</v>
       </c>
       <c r="T57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor 15491-4 TX39A HEB-SIGNED 8-26-26 (awaiting MH signature).pdf</t>
+          <t xml:space="preserve">MH Outdoor 15551-1 TX46B Seguin HEB-SIGNED 8-12-26 (awaiting MH signature).pdf</t>
         </is>
       </c>
       <c r="U57" s="5">
-        <v>1536325</v>
+        <v>166460</v>
       </c>
       <c r="V57" s="9">
-        <v>1200</v>
+        <v>550</v>
       </c>
       <c r="W57" s="9"/>
       <c r="X57" s="5"/>
       <c r="Y57" s="5">
-        <v>4.7</v>
-      </c>
-      <c r="Z57" s="5"/>
+        <v>8.7</v>
+      </c>
+      <c r="Z57" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA57" s="5"/>
       <c r="AB57" s="5"/>
       <c r="AC57" s="7"/>
@@ -5832,22 +6052,22 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX46B</t>
+          <t xml:space="preserve">NT #1302</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor Media</t>
+          <t xml:space="preserve">New Tradition</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandon Wilburn</t>
+          <t xml:space="preserve">Jill Maugle</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bwilburn@machaik.com</t>
+          <t xml:space="preserve">jill@newtradition.com</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -5857,73 +6077,61 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
+          <t xml:space="preserve">Place-Based - Banners ✨</t>
         </is>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/S of Hwy 90 Bus., 600 feet E/o FM 725.    Seguin, Texas N/S, W/F</t>
+          <t xml:space="preserve">Riverwalk – Rivercenter: Banners</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguin</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78155</t>
-        </is>
-      </c>
+          <t xml:space="preserve">San Antonio</t>
+        </is>
+      </c>
+      <c r="J58" s="4"/>
       <c r="K58" s="10">
-        <v>29.555712</v>
+        <v>29.423867</v>
       </c>
       <c r="L58" s="10">
-        <v>-98.027557</v>
-      </c>
-      <c r="M58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+        <v>-98.485107</v>
+      </c>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' x 30'</t>
-        </is>
-      </c>
-      <c r="P58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q58" s="4"/>
+          <t xml:space="preserve">25' H x 10' W Sky Murals (2) ~ 12' H x 2' 6" W Trumpet Banners (10)</t>
+        </is>
+      </c>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New Tradition — Media #1302 Riverwalk/Rivercenter banners (12 units), San Antonio, 8/24–11/1/26, $94,172 — HEB-SIGNED 8/12/26, awaiting NT Credit Dept</t>
+        </is>
+      </c>
       <c r="R58" s="6">
         <v>46258</v>
       </c>
       <c r="S58" s="6">
-        <v>46299</v>
+        <v>46327</v>
       </c>
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MH Outdoor 15551-1 TX46B Seguin HEB-SIGNED 8-12-26 (awaiting MH signature).pdf</t>
+          <t xml:space="preserve">New Tradition 1302 San Antonio HEB-SIGNED 8-12-26 (awaiting NT Credit Dept).pdf</t>
         </is>
       </c>
       <c r="U58" s="4">
-        <v>166460</v>
+        <v>2448716</v>
       </c>
       <c r="V58" s="8">
-        <v>550</v>
+        <v>31186</v>
       </c>
       <c r="W58" s="8"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="Z58" s="12" t="inlineStr">
         <is>
@@ -5938,22 +6146,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NT #1302</t>
+          <t xml:space="preserve">02_6069O</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Tradition</t>
+          <t xml:space="preserve">Outfront Media</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jill Maugle</t>
+          <t xml:space="preserve">Sammy Tamporello</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jill@newtradition.com</t>
+          <t xml:space="preserve">sammy.tamporello@outfront.com</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -5963,76 +6171,88 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Place-Based - Banners ✨</t>
-        </is>
-      </c>
-      <c r="G59" s="5"/>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">535952</t>
+        </is>
+      </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Riverwalk – Rivercenter: Banners</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">San Antonio</t>
-        </is>
-      </c>
+          <t xml:space="preserve">US 281 N .5M S/O Airport Blvd/Loop 410 ES F/N F/N</t>
+        </is>
+      </c>
+      <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="11">
-        <v>29.423867</v>
+        <v>29.51194</v>
       </c>
       <c r="L59" s="11">
-        <v>-98.485107</v>
-      </c>
-      <c r="M59" s="5"/>
+        <v>-98.47541</v>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
       <c r="N59" s="5"/>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">25' H x 10' W Sky Murals (2) ~ 12' H x 2' 6" W Trumpet Banners (10)</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P59" s="5"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Tradition — Media #1302 Riverwalk/Rivercenter banners (12 units), San Antonio, 8/24–11/1/26, $94,172 — HEB-SIGNED 8/12/26, awaiting NT Credit Dept</t>
+          <t xml:space="preserve">281 HV</t>
         </is>
       </c>
       <c r="R59" s="7">
-        <v>46258</v>
+        <v>46209</v>
       </c>
       <c r="S59" s="7">
-        <v>46327</v>
+        <v>46439</v>
       </c>
       <c r="T59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">New Tradition 1302 San Antonio HEB-SIGNED 8-12-26 (awaiting NT Credit Dept).pdf</t>
+          <t xml:space="preserve">Charli Sowrey_encrypted_.pdf</t>
         </is>
       </c>
       <c r="U59" s="5">
-        <v>2448716</v>
+        <v>432834</v>
       </c>
       <c r="V59" s="9">
-        <v>31186</v>
+        <v>7137</v>
       </c>
       <c r="W59" s="9"/>
       <c r="X59" s="5"/>
       <c r="Y59" s="5">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="Z59" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA59" s="5"/>
+      <c r="AA59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB59" s="5"/>
       <c r="AC59" s="7"/>
-      <c r="AD59" s="5"/>
+      <c r="AD59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cowboys: Dak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">02_6069O</t>
+          <t xml:space="preserve">2_1963F</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -6057,26 +6277,30 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">535952</t>
+          <t xml:space="preserve">50769131</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">US 281 N .5M S/O Airport Blvd/Loop 410 ES F/N F/N</t>
+          <t xml:space="preserve">NW Loop 410 W/O Bandera Rd. F/N F/N</t>
         </is>
       </c>
       <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78238</t>
+        </is>
+      </c>
       <c r="K60" s="10">
-        <v>29.51194</v>
+        <v>29.48264</v>
       </c>
       <c r="L60" s="10">
-        <v>-98.47541</v>
+        <v>-98.602335</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
@@ -6086,74 +6310,62 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">14'x48'</t>
         </is>
       </c>
       <c r="P60" s="4"/>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281 HV</t>
-        </is>
-      </c>
+      <c r="Q60" s="4"/>
       <c r="R60" s="6">
-        <v>46209</v>
+        <v>46258</v>
       </c>
       <c r="S60" s="6">
-        <v>46439</v>
+        <v>46327</v>
       </c>
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Charli Sowrey_encrypted_.pdf</t>
+          <t xml:space="preserve">Outfront 4491743 2_1963 SA Digital Bulletin HEB-SIGNED 8-13-26 (awaiting Outfront GM).pdf</t>
         </is>
       </c>
       <c r="U60" s="4">
-        <v>432834</v>
+        <v>1522800</v>
       </c>
       <c r="V60" s="8">
-        <v>7137</v>
+        <v>3500</v>
       </c>
       <c r="W60" s="8"/>
       <c r="X60" s="4"/>
       <c r="Y60" s="4">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z60" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+      <c r="AA60" s="4"/>
       <c r="AB60" s="4"/>
       <c r="AC60" s="6"/>
-      <c r="AD60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
-        </is>
-      </c>
+      <c r="AD60" s="4"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_1963F</t>
+          <t xml:space="preserve">54560.2</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outfront Media</t>
+          <t xml:space="preserve">SignAd</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sammy Tamporello</t>
+          <t xml:space="preserve">Amy Morgan</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sammy.tamporello@outfront.com</t>
+          <t xml:space="preserve">amy@signad.com</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -6166,40 +6378,48 @@
           <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50769131</t>
-        </is>
-      </c>
+      <c r="G61" s="5"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NW Loop 410 W/O Bandera Rd. F/N F/N</t>
-        </is>
-      </c>
-      <c r="I61" s="5"/>
+          <t xml:space="preserve">FM 78/OLD SEGUIN RD/.7 MI E/O WALZEM RD/CONVERSE-LED-LH/WB</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONVERSE</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78238</t>
+          <t xml:space="preserve">78109</t>
         </is>
       </c>
       <c r="K61" s="11">
-        <v>29.48264</v>
+        <v>29.4964</v>
       </c>
       <c r="L61" s="11">
-        <v>-98.602335</v>
+        <v>-98.3239</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
-        </is>
-      </c>
-      <c r="N61" s="5"/>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'x48'</t>
-        </is>
-      </c>
-      <c r="P61" s="5"/>
+          <t xml:space="preserve">10 ft x 36 ft</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="7">
         <v>46258</v>
@@ -6209,19 +6429,19 @@
       </c>
       <c r="T61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outfront 4491743 2_1963 SA Digital Bulletin HEB-SIGNED 8-13-26 (awaiting Outfront GM).pdf</t>
+          <t xml:space="preserve">SignAd 052630 54560.2 Converse LED HEB-SIGNED 8-12-26 (awaiting SignAd officer).pdf</t>
         </is>
       </c>
       <c r="U61" s="5">
-        <v>1522800</v>
+        <v>24119</v>
       </c>
       <c r="V61" s="9">
-        <v>3500</v>
+        <v>1000</v>
       </c>
       <c r="W61" s="9"/>
       <c r="X61" s="5"/>
       <c r="Y61" s="5">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="Z61" s="13" t="inlineStr">
         <is>
@@ -6232,104 +6452,6 @@
       <c r="AB61" s="5"/>
       <c r="AC61" s="7"/>
       <c r="AD61" s="5"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54560.2</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SignAd</t>
-        </is>
-      </c>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">San Antonio</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Digital Bulletin</t>
-        </is>
-      </c>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FM 78/OLD SEGUIN RD/.7 MI E/O WALZEM RD/CONVERSE-LED-LH/WB</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONVERSE</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78109</t>
-        </is>
-      </c>
-      <c r="K62" s="10">
-        <v>29.4964</v>
-      </c>
-      <c r="L62" s="10">
-        <v>-98.3239</v>
-      </c>
-      <c r="M62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">East</t>
-        </is>
-      </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
-      <c r="O62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10 ft x 36 ft</t>
-        </is>
-      </c>
-      <c r="P62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="6">
-        <v>46258</v>
-      </c>
-      <c r="S62" s="6">
-        <v>46327</v>
-      </c>
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SignAd 052630 54560.2 Converse LED HEB-SIGNED 8-12-26 (awaiting SignAd officer).pdf</t>
-        </is>
-      </c>
-      <c r="U62" s="4">
-        <v>24119</v>
-      </c>
-      <c r="V62" s="8">
-        <v>1000</v>
-      </c>
-      <c r="W62" s="8"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4">
-        <v>2.4</v>
-      </c>
-      <c r="Z62" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA62" s="4"/>
-      <c r="AB62" s="4"/>
-      <c r="AC62" s="6"/>
-      <c r="AD62" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AD3"/>
@@ -6365,28 +6487,27 @@
     <hyperlink ref="Z28" r:id="rIdH25"/>
     <hyperlink ref="Z29" r:id="rIdH26"/>
     <hyperlink ref="Z30" r:id="rIdH27"/>
-    <hyperlink ref="Z31" r:id="rIdH28"/>
+    <hyperlink ref="Z33" r:id="rIdH28"/>
     <hyperlink ref="Z34" r:id="rIdH29"/>
     <hyperlink ref="Z35" r:id="rIdH30"/>
     <hyperlink ref="Z36" r:id="rIdH31"/>
-    <hyperlink ref="Z37" r:id="rIdH32"/>
+    <hyperlink ref="Z40" r:id="rIdH32"/>
     <hyperlink ref="Z41" r:id="rIdH33"/>
     <hyperlink ref="Z42" r:id="rIdH34"/>
     <hyperlink ref="Z43" r:id="rIdH35"/>
-    <hyperlink ref="Z44" r:id="rIdH36"/>
+    <hyperlink ref="Z45" r:id="rIdH36"/>
     <hyperlink ref="Z46" r:id="rIdH37"/>
     <hyperlink ref="Z47" r:id="rIdH38"/>
     <hyperlink ref="Z48" r:id="rIdH39"/>
-    <hyperlink ref="Z49" r:id="rIdH40"/>
+    <hyperlink ref="Z50" r:id="rIdH40"/>
     <hyperlink ref="Z51" r:id="rIdH41"/>
-    <hyperlink ref="Z52" r:id="rIdH42"/>
+    <hyperlink ref="Z54" r:id="rIdH42"/>
     <hyperlink ref="Z55" r:id="rIdH43"/>
-    <hyperlink ref="Z56" r:id="rIdH44"/>
+    <hyperlink ref="Z57" r:id="rIdH44"/>
     <hyperlink ref="Z58" r:id="rIdH45"/>
     <hyperlink ref="Z59" r:id="rIdH46"/>
     <hyperlink ref="Z60" r:id="rIdH47"/>
     <hyperlink ref="Z61" r:id="rIdH48"/>
-    <hyperlink ref="Z62" r:id="rIdH49"/>
   </hyperlinks>
 </worksheet>
 </file>